--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -5092,7 +5092,7 @@
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46232.62438284722</v>
+        <v>46279.15118835648</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>216</v>
@@ -5136,8 +5136,8 @@
       <c r="R65" s="9">
         <v>46286</v>
       </c>
-      <c r="S65" s="7" t="s">
-        <v>90</v>
+      <c r="S65" s="12" t="s">
+        <v>210</v>
       </c>
       <c r="T65" s="10">
         <v>0</v>

--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -5257,7 +5257,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46232.624382546295</v>
+        <v>46280.13148483796</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>225</v>
@@ -5301,8 +5301,8 @@
       <c r="R68" s="5">
         <v>46287</v>
       </c>
-      <c r="S68" s="7" t="s">
-        <v>90</v>
+      <c r="S68" s="12" t="s">
+        <v>210</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>

--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46274.14918030093</v>
+        <v>46281.250455</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>208</v>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="C63" s="10"/>
       <c r="D63" s="9">
-        <v>46225.01286980324</v>
+        <v>46281.25045665509</v>
       </c>
       <c r="E63" s="10" t="s">
         <v>147</v>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46225.01288368055</v>
+        <v>46281.250453796296</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>147</v>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46240.82233700232</v>
+        <v>46281.12989119213</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>234</v>
@@ -5470,8 +5470,8 @@
       <c r="R71" s="9">
         <v>46288</v>
       </c>
-      <c r="S71" s="7" t="s">
-        <v>90</v>
+      <c r="S71" s="12" t="s">
+        <v>210</v>
       </c>
       <c r="T71" s="10">
         <v>0</v>

--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -383,6 +383,9 @@
     <t>Control de calidad  OT 4377,Generacion Oc  OT 4377,Armado OT 4377</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1216774111322476</t>
   </si>
   <si>
@@ -666,9 +669,6 @@
   </si>
   <si>
     <t xml:space="preserve">Montaje:,Montaje Alabe OT 4377 </t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1216774225731703</t>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C31" s="10"/>
       <c r="D31" s="9">
-        <v>46225.01064516204</v>
+        <v>46282.139155474535</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>111</v>
@@ -3182,8 +3182,8 @@
       <c r="R31" s="9">
         <v>46247</v>
       </c>
-      <c r="S31" s="7" t="s">
-        <v>90</v>
+      <c r="S31" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="T31" s="10">
         <v>0</v>
@@ -3194,7 +3194,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B32" s="5">
         <v>46225.009524594905</v>
@@ -3204,7 +3204,7 @@
         <v>46255.62865266204</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3234,10 +3234,10 @@
         <v>111</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3247,7 +3247,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B33" s="9">
         <v>46225.0095310301</v>
@@ -3257,7 +3257,7 @@
         <v>46225.010939224536</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>26</v>
@@ -3287,10 +3287,10 @@
         <v>111</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P33" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q33" s="10"/>
       <c r="R33" s="10"/>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B34" s="5">
         <v>46225.009536620375</v>
@@ -3310,16 +3310,16 @@
         <v>46225.01096177084</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I34" s="5">
         <v>46289</v>
@@ -3340,7 +3340,7 @@
         <v>111</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>111</v>
@@ -3353,7 +3353,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B35" s="9">
         <v>46225.00954297454</v>
@@ -3363,7 +3363,7 @@
         <v>46238.4866103588</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>25</v>
@@ -3387,7 +3387,7 @@
         <v>26</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P35" s="10" t="s">
         <v>26</v>
@@ -3400,7 +3400,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B36" s="5">
         <v>46225.00954668982</v>
@@ -3412,16 +3412,16 @@
         <v>46235.19777150463</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I36" s="5">
         <v>46230</v>
@@ -3439,13 +3439,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>46</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q36" s="5">
         <v>46234</v>
@@ -3465,7 +3465,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B37" s="9">
         <v>46225.009553993055</v>
@@ -3477,16 +3477,16 @@
         <v>46242.19777017361</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I37" s="9">
         <v>46237</v>
@@ -3504,13 +3504,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q37" s="9">
         <v>46241</v>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B38" s="5">
         <v>46225.00956064815</v>
@@ -3548,10 +3548,10 @@
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I38" s="5">
         <v>46244</v>
@@ -3569,13 +3569,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q38" s="5">
         <v>46244</v>
@@ -3595,7 +3595,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B39" s="9">
         <v>46225.00957443287</v>
@@ -3605,16 +3605,16 @@
         <v>46225.01576019676</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I39" s="9">
         <v>46290</v>
@@ -3632,13 +3632,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q39" s="9">
         <v>46290</v>
@@ -3658,7 +3658,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B40" s="5">
         <v>46225.00958157408</v>
@@ -3668,16 +3668,16 @@
         <v>46225.01156247685</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I40" s="6"/>
       <c r="J40" s="5">
@@ -3693,13 +3693,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3709,7 +3709,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B41" s="9">
         <v>46225.00958684028</v>
@@ -3719,16 +3719,16 @@
         <v>46225.01157688657</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="9">
@@ -3744,13 +3744,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3760,7 +3760,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B42" s="5">
         <v>46225.00963939815</v>
@@ -3770,7 +3770,7 @@
         <v>46262.51117300926</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3794,7 +3794,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3807,7 +3807,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B43" s="9">
         <v>46225.00968099537</v>
@@ -3817,16 +3817,16 @@
         <v>46261.18440158565</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I43" s="10"/>
       <c r="J43" s="9">
@@ -3842,13 +3842,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O43" s="10" t="s">
         <v>92</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q43" s="9">
         <v>46260</v>
@@ -3868,7 +3868,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B44" s="5">
         <v>46225.009690335646</v>
@@ -3878,16 +3878,16 @@
         <v>46261.18440128472</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I44" s="5">
         <v>46260</v>
@@ -3905,13 +3905,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>100</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q44" s="5">
         <v>46260</v>
@@ -3931,7 +3931,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B45" s="9">
         <v>46225.00969839121</v>
@@ -3941,16 +3941,16 @@
         <v>46261.18440128472</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I45" s="9">
         <v>46260</v>
@@ -3968,13 +3968,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O45" s="10" t="s">
         <v>108</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q45" s="9">
         <v>46260</v>
@@ -3994,7 +3994,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B46" s="5">
         <v>46225.009706550925</v>
@@ -4004,16 +4004,16 @@
         <v>46262.19512304398</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I46" s="5">
         <v>46261</v>
@@ -4031,13 +4031,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q46" s="5">
         <v>46261</v>
@@ -4057,7 +4057,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B47" s="9">
         <v>46225.00971478009</v>
@@ -4069,16 +4069,16 @@
         <v>46262.5111862037</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I47" s="9">
         <v>46261</v>
@@ -4096,13 +4096,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q47" s="9">
         <v>46261</v>
@@ -4122,7 +4122,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B48" s="5">
         <v>46225.00972827546</v>
@@ -4132,16 +4132,16 @@
         <v>46262.19512244213</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I48" s="5">
         <v>46261</v>
@@ -4159,13 +4159,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q48" s="5">
         <v>46261</v>
@@ -4185,7 +4185,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B49" s="9">
         <v>46225.00973607639</v>
@@ -4195,7 +4195,7 @@
         <v>46225.00984827546</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>25</v>
@@ -4219,7 +4219,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4232,7 +4232,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B50" s="5">
         <v>46225.00973990741</v>
@@ -4248,10 +4248,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I50" s="5">
         <v>46262</v>
@@ -4269,13 +4269,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>74</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q50" s="5">
         <v>46266</v>
@@ -4295,7 +4295,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B51" s="9">
         <v>46225.00974854166</v>
@@ -4305,16 +4305,16 @@
         <v>46274.14150798611</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I51" s="9">
         <v>46267</v>
@@ -4332,13 +4332,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q51" s="9">
         <v>46273</v>
@@ -4358,7 +4358,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B52" s="5">
         <v>46225.0097553588</v>
@@ -4368,16 +4368,16 @@
         <v>46273.16869640046</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I52" s="5">
         <v>46267</v>
@@ -4395,13 +4395,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4411,7 +4411,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B53" s="9">
         <v>46225.00976584491</v>
@@ -4421,16 +4421,16 @@
         <v>46273.16869341435</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I53" s="9">
         <v>46267</v>
@@ -4448,13 +4448,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4464,7 +4464,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B54" s="5">
         <v>46225.00980621528</v>
@@ -4474,16 +4474,16 @@
         <v>46275.14099714121</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I54" s="5">
         <v>46274</v>
@@ -4501,13 +4501,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Q54" s="5">
         <v>46274</v>
@@ -4527,7 +4527,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B55" s="9">
         <v>46225.00981328703</v>
@@ -4537,16 +4537,16 @@
         <v>46274.16861446759</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I55" s="9">
         <v>46274</v>
@@ -4564,13 +4564,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -4580,7 +4580,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B56" s="5">
         <v>46225.00982115741</v>
@@ -4590,16 +4590,16 @@
         <v>46274.16861554398</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I56" s="5">
         <v>46274</v>
@@ -4617,13 +4617,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -4633,7 +4633,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B57" s="9">
         <v>46225.00990130787</v>
@@ -4643,7 +4643,7 @@
         <v>46225.010049375</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>25</v>
@@ -4667,7 +4667,7 @@
         <v>26</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P57" s="10" t="s">
         <v>26</v>
@@ -4680,7 +4680,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B58" s="5">
         <v>46225.009905162035</v>
@@ -4690,16 +4690,16 @@
         <v>46232.1720309375</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I58" s="5">
         <v>46230</v>
@@ -4717,13 +4717,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>53</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q58" s="5">
         <v>46231</v>
@@ -4743,7 +4743,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B59" s="9">
         <v>46225.00991375</v>
@@ -4753,16 +4753,16 @@
         <v>46232.172030752314</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I59" s="9">
         <v>46230</v>
@@ -4780,13 +4780,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O59" s="10" t="s">
         <v>58</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q59" s="9">
         <v>46231</v>
@@ -4806,7 +4806,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B60" s="5">
         <v>46225.0099219213</v>
@@ -4816,16 +4816,16 @@
         <v>46232.17203079861</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I60" s="5">
         <v>46230</v>
@@ -4843,13 +4843,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>61</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q60" s="5">
         <v>46231</v>
@@ -4869,7 +4869,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B61" s="9">
         <v>46225.009930162036</v>
@@ -4879,7 +4879,7 @@
         <v>46232.62468724537</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -4903,7 +4903,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -4916,17 +4916,17 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B62" s="5">
         <v>46225.00993398148</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46281.250455</v>
+        <v>46282.15067552083</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -4953,13 +4953,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q62" s="5">
         <v>46281</v>
@@ -4967,8 +4967,8 @@
       <c r="R62" s="5">
         <v>46275</v>
       </c>
-      <c r="S62" s="12" t="s">
-        <v>210</v>
+      <c r="S62" s="11" t="s">
+        <v>32</v>
       </c>
       <c r="T62" s="6">
         <v>0</v>
@@ -4989,7 +4989,7 @@
         <v>46281.25045665509</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
@@ -5016,10 +5016,10 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O63" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P63" s="10" t="s">
         <v>212</v>
@@ -5042,7 +5042,7 @@
         <v>46281.250453796296</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5069,10 +5069,10 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>214</v>
@@ -5122,7 +5122,7 @@
         <v>26</v>
       </c>
       <c r="N65" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O65" s="10" t="s">
         <v>217</v>
@@ -5137,7 +5137,7 @@
         <v>46286</v>
       </c>
       <c r="S65" s="12" t="s">
-        <v>210</v>
+        <v>115</v>
       </c>
       <c r="T65" s="10">
         <v>0</v>
@@ -5158,7 +5158,7 @@
         <v>46238.48662206018</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5209,7 +5209,7 @@
         <v>46238.48661143519</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5287,7 +5287,7 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>226</v>
@@ -5302,7 +5302,7 @@
         <v>46287</v>
       </c>
       <c r="S68" s="12" t="s">
-        <v>210</v>
+        <v>115</v>
       </c>
       <c r="T68" s="6">
         <v>0</v>
@@ -5323,7 +5323,7 @@
         <v>46225.01320763888</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5376,7 +5376,7 @@
         <v>46225.013223182876</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5456,13 +5456,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O71" s="10" t="s">
         <v>235</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q71" s="9">
         <v>46288</v>
@@ -5471,7 +5471,7 @@
         <v>46288</v>
       </c>
       <c r="S71" s="12" t="s">
-        <v>210</v>
+        <v>115</v>
       </c>
       <c r="T71" s="10">
         <v>0</v>
@@ -5492,7 +5492,7 @@
         <v>46238.486621041666</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5545,7 +5545,7 @@
         <v>46238.4866215625</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46240.82233707176</v>
+        <v>46282.139155439814</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>242</v>
@@ -5625,10 +5625,10 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>243</v>
@@ -5639,8 +5639,8 @@
       <c r="R74" s="5">
         <v>46289</v>
       </c>
-      <c r="S74" s="7" t="s">
-        <v>90</v>
+      <c r="S74" s="12" t="s">
+        <v>115</v>
       </c>
       <c r="T74" s="6">
         <v>0</v>
@@ -5661,7 +5661,7 @@
         <v>46225.013478761575</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5714,7 +5714,7 @@
         <v>46225.01351359954</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5794,7 +5794,7 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O77" s="10" t="s">
         <v>249</v>
@@ -5830,7 +5830,7 @@
         <v>46225.0136440625</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5860,7 +5860,7 @@
         <v>243</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>251</v>
@@ -5883,7 +5883,7 @@
         <v>46225.01367180556</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -5913,7 +5913,7 @@
         <v>243</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P79" s="10" t="s">
         <v>253</v>
@@ -6013,7 +6013,7 @@
         <v>255</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P81" s="10" t="s">
         <v>261</v>
@@ -6046,7 +6046,7 @@
         <v>46225.01378356482</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6076,7 +6076,7 @@
         <v>258</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>263</v>
@@ -6099,7 +6099,7 @@
         <v>46225.01379511574</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6129,7 +6129,7 @@
         <v>258</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P83" s="10" t="s">
         <v>265</v>
@@ -6215,7 +6215,7 @@
         <v>46225.013919687495</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6245,7 +6245,7 @@
         <v>267</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P85" s="10" t="s">
         <v>270</v>
@@ -6268,7 +6268,7 @@
         <v>46225.013935787036</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6298,7 +6298,7 @@
         <v>267</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>272</v>
@@ -6327,10 +6327,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H87" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I87" s="9">
         <v>46296</v>
@@ -6351,7 +6351,7 @@
         <v>255</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P87" s="10" t="s">
         <v>255</v>
@@ -6384,16 +6384,16 @@
         <v>46225.014048425925</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I88" s="5">
         <v>46296</v>
@@ -6414,7 +6414,7 @@
         <v>274</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>276</v>
@@ -6437,16 +6437,16 @@
         <v>46225.014061504626</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I89" s="9">
         <v>46296</v>
@@ -6467,7 +6467,7 @@
         <v>274</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P89" s="10" t="s">
         <v>276</v>
@@ -6496,10 +6496,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I90" s="5">
         <v>46297</v>
@@ -6520,7 +6520,7 @@
         <v>255</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>280</v>
@@ -6553,16 +6553,16 @@
         <v>46225.014210312496</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H91" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I91" s="9">
         <v>46297</v>
@@ -6583,7 +6583,7 @@
         <v>279</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P91" s="10" t="s">
         <v>282</v>
@@ -6606,16 +6606,16 @@
         <v>46225.01422244213</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I92" s="5">
         <v>46297</v>
@@ -6636,7 +6636,7 @@
         <v>279</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>284</v>

--- a/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
+++ b/data/50001579-  XEMORTIZ C. MEXICANA.xlsx
@@ -3602,7 +3602,7 @@
       </c>
       <c r="C39" s="10"/>
       <c r="D39" s="9">
-        <v>46283.16599446759</v>
+        <v>46284.20497747685</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>143</v>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="C51" s="10"/>
       <c r="D51" s="9">
-        <v>46274.14150798611</v>
+        <v>46284.20422222222</v>
       </c>
       <c r="E51" s="10" t="s">
         <v>182</v>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46275.14099714121</v>
+        <v>46284.204329699074</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>189</v>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46282.15067552083</v>
+        <v>46284.204394699074</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>209</v>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="C65" s="10"/>
       <c r="D65" s="9">
-        <v>46279.15118835648</v>
+        <v>46284.204732812505</v>
       </c>
       <c r="E65" s="10" t="s">
         <v>216</v>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46280.13148483796</v>
+        <v>46284.20450832176</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>225</v>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="9">
-        <v>46281.12989119213</v>
+        <v>46284.20455953704</v>
       </c>
       <c r="E71" s="10" t="s">
         <v>234</v>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46282.139155439814</v>
+        <v>46284.20461394676</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>242</v>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="9">
-        <v>46232.624382152775</v>
+        <v>46284.204694444445</v>
       </c>
       <c r="E77" s="10" t="s">
         <v>243</v>
@@ -5980,7 +5980,7 @@
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46225.58761383102</v>
+        <v>46284.20502175926</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>258</v>
@@ -6149,7 +6149,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46225.587646631946</v>
+        <v>46284.20505704861</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>267</v>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46225.58766351852</v>
+        <v>46284.20512118055</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>274</v>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46225.587682592595</v>
+        <v>46284.205355694445</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>279</v>
